--- a/Result/RBM_LowDepthQAE_eps=2^-5_nShot=12.xlsx
+++ b/Result/RBM_LowDepthQAE_eps=2^-5_nShot=12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koich\Desktop\Code\DivQCOSDE\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649CD4D7-6397-4B12-BC34-E58E22962D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B11F20-E625-4122-ABF4-CED448E08AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="405" windowWidth="18345" windowHeight="8790" xr2:uid="{8730DC5B-5742-49A9-9164-FF6EA95AD078}"/>
+    <workbookView xWindow="1650" yWindow="2310" windowWidth="18390" windowHeight="9015" xr2:uid="{8730DC5B-5742-49A9-9164-FF6EA95AD078}"/>
   </bookViews>
   <sheets>
     <sheet name="RBM_LowDepthQAE" sheetId="1" r:id="rId1"/>
@@ -77,8 +77,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="180" formatCode="0.000000"/>
-    <numFmt numFmtId="181" formatCode="0.00000"/>
+    <numFmt numFmtId="176" formatCode="0.000000"/>
+    <numFmt numFmtId="177" formatCode="0.00000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -679,10 +679,10 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -745,6 +745,960 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>RBM_LowDepthQAE!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>maxDepth</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>RBM_LowDepthQAE!$J$2:$J$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>RBM_LowDepthQAE!$N$2:$N$10</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>286</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>352</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>576</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>640</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6AA9-46A8-970D-7F16BBAA34EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="565988752"/>
+        <c:axId val="565987792"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="565988752"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="565987792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="565987792"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:min val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="565988752"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>66681</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>190506</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97BF579A-8020-068E-5096-7DF82354EDA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1064,16 +2018,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{453854F1-4FBD-4AEA-85B6-FB1EDDD605AA}">
-  <dimension ref="A1:N901"/>
+  <dimension ref="A1:Q901"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +2070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>8</v>
       </c>
@@ -1159,7 +2115,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>11</v>
       </c>
@@ -1192,7 +2148,7 @@
         <v>2.6084647076070398E-3</v>
       </c>
       <c r="L3" s="4">
-        <f t="shared" ref="L3:L9" si="3">SQRT(AVERAGEIF($A$2:$A$1048576,$J3,$F$2:$F$1048576))</f>
+        <f t="shared" ref="L3:L8" si="3">SQRT(AVERAGEIF($A$2:$A$1048576,$J3,$F$2:$F$1048576))</f>
         <v>3.3990376162112003E-3</v>
       </c>
       <c r="M3" s="2">
@@ -1204,7 +2160,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>16</v>
       </c>
@@ -1249,7 +2205,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>22</v>
       </c>
@@ -1294,7 +2250,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>32</v>
       </c>
@@ -1339,7 +2295,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>45</v>
       </c>
@@ -1383,8 +2339,20 @@
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O7">
+        <f>M7*2.85</f>
+        <v>11256246</v>
+      </c>
+      <c r="P7">
+        <f>N7*2.85</f>
+        <v>1154.25</v>
+      </c>
+      <c r="Q7">
+        <f>O7/1.5</f>
+        <v>7504164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>64</v>
       </c>
@@ -1428,8 +2396,20 @@
         <f t="shared" si="1"/>
         <v>576</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O8">
+        <f>M8*2.85</f>
+        <v>27316224</v>
+      </c>
+      <c r="P8">
+        <f>N8*2.85</f>
+        <v>1641.6000000000001</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>O8/1.5</f>
+        <v>18210816</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>90</v>
       </c>
@@ -1474,7 +2454,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>128</v>
       </c>
@@ -1519,7 +2499,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1546,7 +2526,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1573,7 +2553,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>16</v>
       </c>
@@ -1600,7 +2580,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>22</v>
       </c>
@@ -1627,7 +2607,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>32</v>
       </c>
@@ -1654,7 +2634,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>45</v>
       </c>
@@ -25579,5 +26559,6 @@
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Result/RBM_LowDepthQAE_eps=2^-5_nShot=12.xlsx
+++ b/Result/RBM_LowDepthQAE_eps=2^-5_nShot=12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koich\Desktop\Code\DivQCOSDE\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B11F20-E625-4122-ABF4-CED448E08AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297E0EE0-723E-4978-A6E6-E5ACB85E5699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="2310" windowWidth="18390" windowHeight="9015" xr2:uid="{8730DC5B-5742-49A9-9164-FF6EA95AD078}"/>
+    <workbookView xWindow="765" yWindow="1185" windowWidth="18390" windowHeight="9015" xr2:uid="{8730DC5B-5742-49A9-9164-FF6EA95AD078}"/>
   </bookViews>
   <sheets>
     <sheet name="RBM_LowDepthQAE" sheetId="1" r:id="rId1"/>
@@ -2339,18 +2339,6 @@
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="O7">
-        <f>M7*2.85</f>
-        <v>11256246</v>
-      </c>
-      <c r="P7">
-        <f>N7*2.85</f>
-        <v>1154.25</v>
-      </c>
-      <c r="Q7">
-        <f>O7/1.5</f>
-        <v>7504164</v>
-      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8">
@@ -2396,18 +2384,7 @@
         <f t="shared" si="1"/>
         <v>576</v>
       </c>
-      <c r="O8">
-        <f>M8*2.85</f>
-        <v>27316224</v>
-      </c>
-      <c r="P8">
-        <f>N8*2.85</f>
-        <v>1641.6000000000001</v>
-      </c>
-      <c r="Q8" s="2">
-        <f>O8/1.5</f>
-        <v>18210816</v>
-      </c>
+      <c r="Q8" s="2"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9">
